--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 51 clubs short</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1079,8 +1079,8 @@
       <c r="R4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="9" t="n">
-        <v>1</v>
+      <c r="S4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T4" s="9" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="X16" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2543,8 +2543,8 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>3</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7405,8 +7405,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7493,8 +7493,8 @@
       <c r="V70" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W70" s="9" t="n">
-        <v>3</v>
+      <c r="W70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>7</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9131,10 +9131,10 @@
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
@@ -9636,8 +9636,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="9" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9733,8 +9733,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -12711,16 +12711,16 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124" s="9" t="n">
         <v>0</v>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13698,8 +13698,8 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>3</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>1</v>
@@ -13999,7 +13999,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14098,7 +14098,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14428,7 +14428,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -14560,7 +14560,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14593,7 +14593,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14857,7 +14857,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 51 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 29 clubs short</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1082,8 +1082,8 @@
       <c r="S4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T4" s="9" t="n">
-        <v>0</v>
+      <c r="T4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U4" s="9" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1294,8 +1294,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>0</v>
@@ -1676,8 +1676,8 @@
       <c r="W10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>3</v>
+      <c r="X10" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2846,8 +2846,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3034,8 +3034,8 @@
       <c r="W24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>0</v>
+      <c r="X24" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3913,8 +3913,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
         <v>0</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U46" s="9" t="n">
         <v>0</v>
@@ -5174,8 +5174,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5756,8 +5756,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>0</v>
@@ -6320,8 +6320,8 @@
       <c r="S58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="9" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7308,8 +7308,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="P70" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q70" s="10" t="n">
         <v>2</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7599,8 +7599,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7793,8 +7793,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="9" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8472,8 +8472,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -8654,8 +8654,8 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>2</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="9" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9713,7 +9713,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="9" t="n">
         <v>0</v>
@@ -9927,8 +9927,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="9" t="n">
         <v>0</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="9" t="n">
         <v>0</v>
@@ -11770,8 +11770,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="9" t="n">
         <v>0</v>
@@ -12158,8 +12158,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="9" t="n">
         <v>0</v>
@@ -12908,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13613,8 +13613,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13999,7 +13999,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14131,7 +14131,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -14197,7 +14197,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14296,7 +14296,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14329,7 +14329,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14362,7 +14362,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14428,7 +14428,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -14527,7 +14527,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14626,7 +14626,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14857,7 +14857,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -12,8 +12,8 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 29 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA136"/>
+  <dimension ref="A1:AA137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1335,17 +1335,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="7" t="n">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1576,8 +1576,8 @@
       <c r="V9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>3</v>
+      <c r="W9" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>2</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>0</v>
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="7" t="n">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="10" t="n">
         <v>2</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>6</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>64</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3516,8 +3516,8 @@
       <c r="V29" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>1</v>
+      <c r="W29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>7</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3663,17 +3663,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
@@ -3711,7 +3711,7 @@
         <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>6</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>7</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>3</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>7</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="P40" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4633,17 +4633,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>64</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>11</v>
+        <v>-12</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>6</v>
@@ -5603,17 +5603,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6088,17 +6088,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="7" t="n">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="7" t="n">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,17 +6670,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -6714,8 +6714,8 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>1</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6767,17 +6767,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="7" t="n">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7393,8 +7393,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>0</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>4</v>
       </c>
       <c r="W70" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>7</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8249,10 +8249,10 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8363,8 +8363,8 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>3</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -8513,17 +8513,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L81" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="7" t="n">
@@ -8752,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -9095,17 +9095,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="7" t="n">
@@ -9192,17 +9192,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L88" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="7" t="n">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9909,14 +9909,14 @@
       <c r="S95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T95" s="9" t="n">
-        <v>0</v>
+      <c r="T95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>2</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -9968,17 +9968,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L97" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="7" t="n">
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -10938,17 +10938,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="7" t="n">
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q110" s="10" t="n">
         <v>2</v>
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11470,8 +11470,8 @@
       <c r="V111" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W111" s="9" t="n">
-        <v>3</v>
+      <c r="W111" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X111" s="9" t="n">
         <v>1</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="7" t="n">
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -11882,19 +11882,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1150549</v>
+        <v>28680960</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Andeesheh Toastmasters Club</t>
+          <t>AI Learners</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -11935,37 +11935,37 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="10" t="n">
-        <v>7</v>
+      <c r="X116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="10" t="n">
-        <v>1</v>
+      <c r="Z116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>4976</v>
+        <v>1150549</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Berkeley Bay</t>
+          <t>Andeesheh Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12032,16 +12032,16 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" s="10" t="n">
         <v>1</v>
@@ -12050,13 +12050,13 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>791318</v>
+        <v>4976</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Bioradical Toastmasters Club</t>
+          <t>Berkeley Bay</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,25 +12102,25 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O118" s="8" t="inlineStr">
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
@@ -12147,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12161,8 +12161,8 @@
       <c r="Z118" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA118" s="9" t="n">
-        <v>0</v>
+      <c r="AA118" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>5706</v>
+        <v>791318</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Chevron Refined Speakers Toastmasters Club</t>
+          <t>Bioradical Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,17 +12199,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M119" s="7" t="n">
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12237,26 +12237,26 @@
       <c r="S119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="9" t="n">
-        <v>3</v>
+      <c r="X119" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="9" t="n">
         <v>0</v>
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>1507</v>
+        <v>5706</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>El Cerrito Toastmasters</t>
+          <t>Chevron Refined Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -12310,11 +12310,11 @@
         </is>
       </c>
       <c r="M120" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O120" s="8" t="inlineStr">
@@ -12341,22 +12341,22 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="10" t="n">
-        <v>7</v>
+      <c r="X120" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA120" s="10" t="n">
-        <v>1</v>
+      <c r="Z120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -12371,11 +12371,11 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>1619968</v>
+        <v>1507</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Healthy Toasts</t>
+          <t>El Cerrito Toastmasters</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L121" s="8" t="inlineStr">
         <is>
@@ -12438,13 +12438,13 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12464,19 +12464,19 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1130768</v>
+        <v>1619968</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Marin Improv Toastmasters</t>
+          <t>Healthy Toasts</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12493,10 +12493,10 @@
         <v>9</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -12540,14 +12540,14 @@
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="9" t="n">
-        <v>3</v>
+      <c r="X122" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12565,11 +12565,11 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>890</v>
+        <v>1130768</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Marin Toastmasters 890</t>
+          <t>Marin Improv Toastmasters</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -12587,25 +12587,25 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O123" s="8" t="inlineStr">
@@ -12638,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="X123" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12646,8 +12646,8 @@
       <c r="Z123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA123" s="9" t="n">
-        <v>0</v>
+      <c r="AA123" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>635</v>
+        <v>890</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Pitch Perfect Toastmasters</t>
+          <t>Marin Toastmasters 890</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -12698,11 +12698,11 @@
         </is>
       </c>
       <c r="M124" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O124" s="8" t="inlineStr">
@@ -12711,16 +12711,16 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T124" s="9" t="n">
         <v>0</v>
@@ -12728,14 +12728,14 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>0</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="10" t="n">
-        <v>7</v>
+      <c r="X124" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12743,8 +12743,8 @@
       <c r="Z124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA124" s="10" t="n">
-        <v>1</v>
+      <c r="AA124" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1441</v>
+        <v>635</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Southern Marin Toastmasters Club</t>
+          <t>Pitch Perfect Toastmasters</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
@@ -12808,16 +12808,16 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -12825,20 +12825,20 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="10" t="n">
-        <v>4</v>
+      <c r="V125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="10" t="n">
-        <v>1</v>
+      <c r="Z125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7359</v>
+        <v>1441</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Toast of Petaluma</t>
+          <t>Southern Marin Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -12916,20 +12916,20 @@
       <c r="S126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T126" s="9" t="n">
-        <v>0</v>
+      <c r="T126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>2</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -12949,19 +12949,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>4069</v>
+        <v>7359</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Downtown Toastmasters</t>
+          <t>Toast of Petaluma</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13005,28 +13005,28 @@
         <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="9" t="n">
-        <v>3</v>
+      <c r="X127" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1352866</v>
+        <v>4069</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Kaiser Communicators</t>
+          <t>Downtown Toastmasters</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
@@ -13086,11 +13086,11 @@
         </is>
       </c>
       <c r="M128" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O128" s="8" t="inlineStr">
@@ -13117,22 +13117,22 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA128" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>182</v>
+        <v>1352866</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Santa Rosa Club</t>
+          <t>Kaiser Communicators</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,25 +13169,25 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O129" s="8" t="inlineStr">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -13214,22 +13214,22 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="10" t="n">
-        <v>5</v>
+      <c r="X129" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA129" s="10" t="n">
-        <v>1</v>
+      <c r="Z129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>1449647</v>
+        <v>182</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>The Daybreakers</t>
+          <t>Santa Rosa Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-18</v>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13322,8 +13322,8 @@
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13341,11 +13341,11 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>5434039</v>
+        <v>1449647</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Toast Tronic</t>
+          <t>The Daybreakers</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K131" s="4" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>0</v>
@@ -13408,13 +13408,13 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="9" t="n">
-        <v>0</v>
+      <c r="X131" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13434,15 +13434,15 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>8886</v>
+        <v>5434039</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Cloverdale Toastmasters Club 8886</t>
+          <t>Toast Tronic</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L132" s="8" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>0</v>
       </c>
       <c r="X132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>6627</v>
+        <v>8886</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Fountaingrove Club</t>
+          <t>Cloverdale Toastmasters Club 8886</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,17 +13557,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L133" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
@@ -13587,7 +13587,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13602,19 +13602,19 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="10" t="n">
-        <v>5</v>
+      <c r="X133" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="10" t="n">
-        <v>1</v>
+      <c r="Z133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13632,11 +13632,11 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>6561</v>
+        <v>6627</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Lunch-Bunch Toastmasters Club</t>
+          <t>Fountaingrove Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13668,11 +13668,11 @@
         </is>
       </c>
       <c r="M134" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O134" s="8" t="inlineStr">
@@ -13684,7 +13684,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -13698,23 +13698,23 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="10" t="n">
-        <v>4</v>
+      <c r="V134" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>1</v>
+      <c r="X134" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -13729,11 +13729,11 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>8731</v>
+        <v>6561</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Tenacious Talkers Club</t>
+          <t>Lunch-Bunch Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -13765,11 +13765,11 @@
         </is>
       </c>
       <c r="M135" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O135" s="8" t="inlineStr">
@@ -13795,23 +13795,23 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>1</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X135" s="10" t="n">
-        <v>5</v>
+      <c r="X135" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA135" s="10" t="n">
-        <v>1</v>
+      <c r="Z135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>5622</v>
+        <v>8731</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Ukiah Toastmasters</t>
+          <t>Tenacious Talkers Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,17 +13848,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="7" t="n">
@@ -13875,44 +13875,141 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA136" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>5622</v>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Ukiah Toastmasters</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" s="10" t="n">
+      <c r="F137" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J137" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K137" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M137" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O137" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P137" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" s="9" t="n">
+      <c r="T137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" s="10" t="n">
+      <c r="W137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Y136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA136" s="10" t="n">
+      <c r="Y137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA136"/>
+  <autoFilter ref="A1:AA137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13923,7 +14020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14032,7 +14129,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14047,7 +14144,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -14113,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -14146,7 +14243,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -14164,7 +14261,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -14212,7 +14309,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -14278,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -14344,7 +14441,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -14377,7 +14474,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14395,7 +14492,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14410,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14428,7 +14525,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14443,7 +14540,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -14527,7 +14624,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14542,7 +14639,7 @@
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -14575,7 +14672,7 @@
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14593,7 +14690,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14641,7 +14738,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -14674,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -14707,7 +14804,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -14725,7 +14822,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14740,7 +14837,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -14751,29 +14848,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -14784,29 +14881,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6</v>
+        <v>1.33</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -14817,14 +14914,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14850,14 +14947,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -14872,11 +14969,44 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>6</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="9" t="n">
         <v>0</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>64</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>4</v>
       </c>
       <c r="W29" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>7</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3604,8 +3604,8 @@
       <c r="S30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T30" s="9" t="n">
-        <v>0</v>
+      <c r="T30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U30" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>0</v>
@@ -6357,11 +6357,11 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>2512526</v>
+        <v>28680960</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>FiDi Toastmasters</t>
+          <t>AI Learners</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -6379,17 +6379,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M59" s="7" t="n">
@@ -6429,8 +6429,8 @@
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="10" t="n">
-        <v>5</v>
+      <c r="X59" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6454,11 +6454,11 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>28675364</v>
+        <v>2512526</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Lighthouse Visionaries</t>
+          <t>FiDi Toastmasters</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6526,8 +6526,8 @@
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="9" t="n">
-        <v>3</v>
+      <c r="X60" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -6551,15 +6551,15 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>822664</v>
+        <v>28675364</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Rainbow Toastmasters</t>
+          <t>Lighthouse Visionaries</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6629,8 +6629,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="10" t="n">
-        <v>1</v>
+      <c r="Z61" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6648,15 +6648,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>9109</v>
+        <v>822664</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Rhino Toastmasters</t>
+          <t>Rainbow Toastmasters</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -6697,31 +6697,31 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X62" s="10" t="n">
-        <v>5</v>
+      <c r="X62" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
@@ -6745,15 +6745,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1488281</v>
+        <v>9109</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Salesforce Toastmasters</t>
+          <t>Rhino Toastmasters</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -6811,14 +6811,14 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>3</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X63" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
@@ -6838,19 +6838,19 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>600229</v>
+        <v>1488281</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Civic Center Toastmasters</t>
+          <t>Salesforce Toastmasters</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -6878,11 +6878,11 @@
         </is>
       </c>
       <c r="M64" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O64" s="8" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -6909,22 +6909,22 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X64" s="9" t="n">
-        <v>0</v>
+      <c r="X64" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -6939,15 +6939,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1244</v>
+        <v>600229</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Fightin' 49ers Club</t>
+          <t>Civic Center Toastmasters</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -6975,11 +6975,11 @@
         </is>
       </c>
       <c r="M65" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O65" s="8" t="inlineStr">
@@ -6991,13 +6991,13 @@
         <v>0</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -7006,22 +7006,22 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="10" t="n">
-        <v>1</v>
+      <c r="Z65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -7036,39 +7036,39 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2258108</v>
+        <v>1244</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>San Francisco Mandarin English</t>
+          <t>Fightin' 49ers Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K66" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K66" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="7" t="n">
@@ -7085,31 +7085,31 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T66" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X66" s="10" t="n">
-        <v>7</v>
+      <c r="X66" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7133,15 +7133,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>5610</v>
+        <v>2258108</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Sierra Speakers Toastmasters</t>
+          <t>San Francisco Mandarin English</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L67" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M67" s="7" t="n">
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7199,14 +7199,14 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>1</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X67" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7230,15 +7230,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>3030595</v>
+        <v>5610</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters For Health</t>
+          <t>Sierra Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7290,20 +7290,20 @@
       <c r="S68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T68" s="9" t="n">
-        <v>0</v>
+      <c r="T68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="9" t="n">
-        <v>0</v>
+      <c r="X68" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -7327,15 +7327,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>7222873</v>
+        <v>3030595</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Uber San Francisco Club</t>
+          <t>Toastmasters For Health</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7352,10 +7352,10 @@
         <v>8</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7393,8 +7393,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="10" t="n">
-        <v>4</v>
+      <c r="V69" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7415,24 +7415,24 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>3756371</v>
+        <v>7222873</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>City Speech Toastmasters</t>
+          <t>Uber San Francisco Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7446,17 +7446,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="7" t="n">
@@ -7472,20 +7472,20 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P70" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q70" s="10" t="n">
-        <v>2</v>
+      <c r="P70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T70" s="10" t="n">
-        <v>1</v>
+      <c r="S70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
@@ -7493,11 +7493,11 @@
       <c r="V70" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W70" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X70" s="10" t="n">
-        <v>7</v>
+      <c r="W70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7521,15 +7521,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>28680443</v>
+        <v>3756371</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Once Upon A Speech</t>
+          <t>City Speech Toastmasters</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7569,32 +7569,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="9" t="n">
-        <v>0</v>
+      <c r="P71" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q71" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" s="9" t="n">
-        <v>0</v>
+      <c r="S71" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W71" s="9" t="n">
-        <v>0</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W71" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -7618,15 +7618,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>28676256</v>
+        <v>28680443</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Toastmasters (RAT)</t>
+          <t>Once Upon A Speech</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7640,17 +7640,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M72" s="7" t="n">
@@ -7667,16 +7667,16 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -7685,19 +7685,19 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>2</v>
+      <c r="X72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -7715,15 +7715,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>5350671</v>
+        <v>28676256</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Rocketelectric Toasters</t>
+          <t>Regulatory Affairs Toastmasters (RAT)</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -7782,19 +7782,19 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X73" s="10" t="n">
-        <v>4</v>
+      <c r="X73" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="10" t="n">
-        <v>1</v>
+      <c r="Z73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -7812,11 +7812,11 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2760</v>
+        <v>5350671</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>South Bay Toastmasters</t>
+          <t>Rocketelectric Toasters</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -7905,15 +7905,15 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>654714</v>
+        <v>2760</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Citizens for Better Communicators Club</t>
+          <t>South Bay Toastmasters</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -7976,13 +7976,13 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8006,15 +8006,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>9338</v>
+        <v>654714</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Speakers Forum Toastmasters</t>
+          <t>Citizens for Better Communicators Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="7" t="n">
@@ -8055,16 +8055,16 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q76" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q76" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="10" t="n">
-        <v>2</v>
+      <c r="S76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8103,15 +8103,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>5067</v>
+        <v>9338</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Star Search Club</t>
+          <t>Speakers Forum Toastmasters</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J77" s="4" t="n">
         <v>27</v>
-      </c>
-      <c r="J77" s="4" t="n">
-        <v>28</v>
       </c>
       <c r="K77" s="4" t="n">
         <v>-1</v>
@@ -8154,14 +8154,14 @@
       <c r="P77" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q77" s="9" t="n">
-        <v>0</v>
+      <c r="Q77" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="9" t="n">
-        <v>0</v>
+      <c r="S77" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T77" s="9" t="n">
         <v>0</v>
@@ -8169,11 +8169,11 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="10" t="n">
-        <v>4</v>
+      <c r="V77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -8200,15 +8200,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>5269</v>
+        <v>5067</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Union City Toastmasters Club</t>
+          <t>Star Search Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8222,25 +8222,25 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K78" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M78" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O78" s="8" t="inlineStr">
@@ -8252,7 +8252,7 @@
         <v>2</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
@@ -8266,14 +8266,14 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>0</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8281,8 +8281,8 @@
       <c r="Z78" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA78" s="9" t="n">
-        <v>0</v>
+      <c r="AA78" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8293,63 +8293,63 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>595243</v>
+        <v>5269</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>F.A.T. Toastmasters Club</t>
+          <t>Union City Toastmasters Club</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P79" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F79" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M79" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N79" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O79" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P79" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8363,14 +8363,14 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="10" t="n">
-        <v>4</v>
+      <c r="V79" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8378,8 +8378,8 @@
       <c r="Z79" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA79" s="10" t="n">
-        <v>1</v>
+      <c r="AA79" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -8394,15 +8394,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>682</v>
+        <v>595243</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Fantastic Toastmasters</t>
+          <t>F.A.T. Toastmasters Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8416,17 +8416,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M80" s="7" t="n">
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>0</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>3</v>
+      <c r="X80" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8491,11 +8491,11 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1118</v>
+        <v>682</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Newark Toastmasters Club</t>
+          <t>Fantastic Toastmasters</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>-2</v>
@@ -8558,13 +8558,13 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="10" t="n">
-        <v>5</v>
+      <c r="X81" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -8588,11 +8588,11 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>4657</v>
+        <v>1118</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>T*Toasters Club</t>
+          <t>Newark Toastmasters Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -8610,67 +8610,67 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J82" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="K82" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M82" s="7" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N82" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O82" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA82" s="9" t="n">
-        <v>0</v>
+      <c r="AA82" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8685,15 +8685,15 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>28677175</v>
+        <v>4657</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>US Biopharma</t>
+          <t>T*Toasters Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -8751,20 +8751,20 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>1</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>2</v>
+      <c r="X83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="9" t="n">
         <v>0</v>
@@ -8778,15 +8778,15 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>8597</v>
+        <v>28677175</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>A Cut Above Club</t>
+          <t>US Biopharma</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -8818,11 +8818,11 @@
         </is>
       </c>
       <c r="M84" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O84" s="8" t="inlineStr">
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -8849,13 +8849,13 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="10" t="n">
-        <v>5</v>
+      <c r="X84" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -8863,8 +8863,8 @@
       <c r="Z84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA84" s="10" t="n">
-        <v>1</v>
+      <c r="AA84" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -8879,11 +8879,11 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>207</v>
+        <v>8597</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Bayfair Toastmasters Club</t>
+          <t>A Cut Above Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -8915,11 +8915,11 @@
         </is>
       </c>
       <c r="M85" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O85" s="8" t="inlineStr">
@@ -8931,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
@@ -8951,8 +8951,8 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="9" t="n">
-        <v>0</v>
+      <c r="X85" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
@@ -8960,8 +8960,8 @@
       <c r="Z85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA85" s="9" t="n">
-        <v>0</v>
+      <c r="AA85" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -8976,15 +8976,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>961</v>
+        <v>207</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Castro Valley Toastmasters Club #961</t>
+          <t>Bayfair Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9012,11 +9012,11 @@
         </is>
       </c>
       <c r="M86" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O86" s="8" t="inlineStr">
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9036,8 +9036,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="10" t="n">
-        <v>1</v>
+      <c r="T86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9048,17 +9048,17 @@
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="10" t="n">
-        <v>4</v>
+      <c r="X86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA86" s="10" t="n">
-        <v>1</v>
+      <c r="Z86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -9073,11 +9073,11 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>4641440</v>
+        <v>961</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>GenoMasters</t>
+          <t>Castro Valley Toastmasters Club #961</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" s="10" t="n">
         <v>1</v>
@@ -9140,13 +9140,13 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9170,15 +9170,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>3442284</v>
+        <v>4641440</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Stagecoach Warriors</t>
+          <t>GenoMasters</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9219,31 +9219,31 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X88" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9267,11 +9267,11 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>3137</v>
+        <v>3442284</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Top of the Hill Toastmasters Club</t>
+          <t>Stagecoach Warriors</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
@@ -9303,11 +9303,11 @@
         </is>
       </c>
       <c r="M89" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O89" s="8" t="inlineStr">
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9327,20 +9327,20 @@
       <c r="S89" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T89" s="10" t="n">
-        <v>1</v>
+      <c r="T89" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9348,8 +9348,8 @@
       <c r="Z89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA89" s="9" t="n">
-        <v>0</v>
+      <c r="AA89" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1940417</v>
+        <v>3137</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Alameda Tongue Twisters</t>
+          <t>Top of the Hill Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>-2</v>
@@ -9400,11 +9400,11 @@
         </is>
       </c>
       <c r="M90" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O90" s="8" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -9422,7 +9422,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" s="10" t="n">
         <v>1</v>
@@ -9431,13 +9431,13 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -9445,8 +9445,8 @@
       <c r="Z90" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA90" s="10" t="n">
-        <v>1</v>
+      <c r="AA90" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -9461,11 +9461,11 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>6781</v>
+        <v>1940417</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Coastmasters</t>
+          <t>Alameda Tongue Twisters</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -9528,13 +9528,13 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -9558,15 +9558,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>28677036</v>
+        <v>6781</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>ExelOrators</t>
+          <t>Coastmasters</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,25 +9580,25 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O92" s="8" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
@@ -9618,20 +9618,20 @@
       <c r="S92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>0</v>
+      <c r="X92" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -9639,8 +9639,8 @@
       <c r="Z92" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA92" s="9" t="n">
-        <v>0</v>
+      <c r="AA92" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -9655,15 +9655,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>5229</v>
+        <v>28677036</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Island City Toastmasters Club</t>
+          <t>ExelOrators</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,25 +9677,25 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M93" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O93" s="8" t="inlineStr">
@@ -9713,7 +9713,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -9722,13 +9722,13 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X93" s="10" t="n">
-        <v>6</v>
+      <c r="X93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -9736,8 +9736,8 @@
       <c r="Z93" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA93" s="10" t="n">
-        <v>1</v>
+      <c r="AA93" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -9752,15 +9752,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>452</v>
+        <v>5229</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>San Leandro Toastmasters Club</t>
+          <t>Island City Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -9788,11 +9788,11 @@
         </is>
       </c>
       <c r="M94" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O94" s="8" t="inlineStr">
@@ -9804,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
@@ -9819,13 +9819,13 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X94" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -9833,8 +9833,8 @@
       <c r="Z94" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA94" s="9" t="n">
-        <v>0</v>
+      <c r="AA94" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>6605</v>
+        <v>452</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Windmaster Club</t>
+          <t>San Leandro Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -9901,28 +9901,28 @@
         <v>0</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="10" t="n">
+      <c r="V95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -9937,24 +9937,24 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>9389</v>
+        <v>6605</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>East Bay Toastmasters Club</t>
+          <t>Windmaster Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -9982,11 +9982,11 @@
         </is>
       </c>
       <c r="M96" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O96" s="8" t="inlineStr">
@@ -10006,20 +10006,20 @@
       <c r="S96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T96" s="9" t="n">
-        <v>0</v>
+      <c r="T96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>1</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="10" t="n">
-        <v>5</v>
+      <c r="X96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10027,8 +10027,8 @@
       <c r="Z96" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA96" s="10" t="n">
-        <v>1</v>
+      <c r="AA96" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -10043,15 +10043,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1463058</v>
+        <v>9389</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Heart2Heart</t>
+          <t>East Bay Toastmasters Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10103,20 +10103,20 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" s="10" t="n">
-        <v>1</v>
+      <c r="T97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10140,15 +10140,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>2767</v>
+        <v>1463058</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Lakeview Toastmasters Club</t>
+          <t>Heart2Heart</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10176,11 +10176,11 @@
         </is>
       </c>
       <c r="M98" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O98" s="8" t="inlineStr">
@@ -10200,11 +10200,11 @@
       <c r="S98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V98" s="9" t="n">
         <v>2</v>
@@ -10213,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10221,8 +10221,8 @@
       <c r="Z98" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA98" s="9" t="n">
-        <v>0</v>
+      <c r="AA98" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -10237,15 +10237,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>88</v>
+        <v>2767</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Oakland 88 Toastmasters Club</t>
+          <t>Lakeview Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10273,11 +10273,11 @@
         </is>
       </c>
       <c r="M99" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O99" s="8" t="inlineStr">
@@ -10289,7 +10289,7 @@
         <v>0</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10304,13 +10304,13 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10318,8 +10318,8 @@
       <c r="Z99" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA99" s="10" t="n">
-        <v>1</v>
+      <c r="AA99" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -10334,15 +10334,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>5409</v>
+        <v>88</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Rockridge Toastmasters Club</t>
+          <t>Oakland 88 Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,17 +10356,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="7" t="n">
@@ -10386,28 +10386,28 @@
         <v>0</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T100" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X100" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -10427,19 +10427,19 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>7831018</v>
+        <v>5409</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Leaders Worldwide</t>
+          <t>Rockridge Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,17 +10453,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="7" t="n">
@@ -10489,28 +10489,28 @@
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X101" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1250</v>
+        <v>7831018</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Oakland City Center Toastmasters Club</t>
+          <t>Leaders Worldwide</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -10595,19 +10595,19 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="10" t="n">
-        <v>1</v>
+      <c r="Z102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>2188234</v>
+        <v>1250</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Scopemasters East Bay</t>
+          <t>Oakland City Center Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L103" s="8" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -10685,8 +10685,8 @@
       <c r="S103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="10" t="n">
-        <v>1</v>
+      <c r="T103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -10698,7 +10698,7 @@
         <v>0</v>
       </c>
       <c r="X103" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>1073164</v>
+        <v>2188234</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Shield Speaks Toastmasters Club</t>
+          <t>Scopemasters East Bay</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -10782,26 +10782,26 @@
       <c r="S104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>0</v>
+      <c r="X104" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10819,15 +10819,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>910103</v>
+        <v>1073164</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Leadership Club</t>
+          <t>Shield Speaks Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -10879,26 +10879,26 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U105" s="10" t="n">
-        <v>1</v>
+      <c r="T105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="10" t="n">
-        <v>7</v>
+      <c r="X105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="10" t="n">
-        <v>1</v>
+      <c r="Z105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -10912,15 +10912,15 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1239</v>
+        <v>910103</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Emeryville Toastmasters</t>
+          <t>Toastmasters Leadership Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -10965,28 +10965,28 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q106" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V106" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>7</v>
@@ -11013,15 +11013,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>4565860</v>
+        <v>1239</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurial Toastmasters</t>
+          <t>Emeryville Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11062,16 +11062,16 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q107" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" s="9" t="n">
         <v>0</v>
@@ -11079,20 +11079,20 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>0</v>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="X107" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>4723864</v>
+        <v>4565860</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Toast On the Hill</t>
+          <t>Entrepreneurial Toastmasters</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11177,19 +11177,19 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="10" t="n">
-        <v>1</v>
+      <c r="Z108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11207,15 +11207,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>5306</v>
+        <v>4723864</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters on Campus Club</t>
+          <t>Toast On the Hill</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11243,11 +11243,11 @@
         </is>
       </c>
       <c r="M109" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O109" s="8" t="inlineStr">
@@ -11280,16 +11280,16 @@
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA109" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -11304,89 +11304,89 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>6061</v>
+        <v>5306</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Warehouse Toastmasters</t>
+          <t>Toastmasters on Campus Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J110" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K110" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M110" s="7" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O110" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F110" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J110" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K110" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M110" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N110" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O110" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P110" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q110" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V110" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -11397,63 +11397,63 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28678424</v>
+        <v>6061</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Clot Masters</t>
+          <t>Warehouse Toastmasters</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J111" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K111" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M111" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O111" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P111" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F111" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G111" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J111" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="K111" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M111" s="7" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N111" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O111" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="9" t="n">
-        <v>0</v>
+      <c r="Q111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -11461,20 +11461,20 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W111" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X111" s="9" t="n">
-        <v>1</v>
+      <c r="V111" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11482,8 +11482,8 @@
       <c r="Z111" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA111" s="9" t="n">
-        <v>0</v>
+      <c r="AA111" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -11498,15 +11498,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>2527</v>
+        <v>28678424</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>East Bay Municipal Utility Dist Toastmasters Club</t>
+          <t>Clot Masters</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11523,10 +11523,10 @@
         <v>20</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11564,14 +11564,14 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" s="10" t="n">
-        <v>7</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W112" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X112" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -11595,15 +11595,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2967</v>
+        <v>2527</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Lakeside Speakeasy Club</t>
+          <t>East Bay Municipal Utility Dist Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,25 +11617,25 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L113" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M113" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O113" s="8" t="inlineStr">
@@ -11647,7 +11647,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11676,8 +11676,8 @@
       <c r="Z113" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA113" s="10" t="n">
-        <v>1</v>
+      <c r="AA113" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>4293</v>
+        <v>2967</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Oakland Uptown Toastmasters</t>
+          <t>Lakeside Speakeasy Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -11728,11 +11728,11 @@
         </is>
       </c>
       <c r="M114" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O114" s="8" t="inlineStr">
@@ -11759,13 +11759,13 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>1</v>
+      <c r="X114" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -11773,8 +11773,8 @@
       <c r="Z114" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA114" s="9" t="n">
-        <v>0</v>
+      <c r="AA114" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -11789,11 +11789,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>28677474</v>
+        <v>4293</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Toothmasters</t>
+          <t>Oakland Uptown Toastmasters</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -11856,19 +11856,19 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="9" t="n">
         <v>0</v>
@@ -11877,20 +11877,20 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28680960</v>
+        <v>28677474</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>AI Learners</t>
+          <t>Toothmasters</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -11908,25 +11908,25 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L116" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O116" s="8" t="inlineStr">
@@ -11967,8 +11967,8 @@
       <c r="Z116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA116" s="10" t="n">
-        <v>1</v>
+      <c r="AA116" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12040,8 +12040,8 @@
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="9" t="n">
-        <v>1</v>
+      <c r="S117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T117" s="10" t="n">
         <v>1</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="8" t="inlineStr">
         <is>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12905,16 +12905,16 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" s="10" t="n">
         <v>1</v>
@@ -12926,7 +12926,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>6</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14294,7 +14294,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14489,16 +14489,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -14507,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -14525,7 +14525,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14848,26 +14848,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -14881,29 +14881,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14936,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -14947,14 +14947,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -14969,44 +14969,11 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:I28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/205/inyear.xlsx
+++ b/docs/d/205/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>6</v>
@@ -3305,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3666,10 +3666,10 @@
         <v>19</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>1</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="10" t="n">
         <v>1</v>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>-1</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4927,10 +4927,10 @@
         <v>21</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7087,8 +7087,8 @@
       <c r="P66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" s="9" t="n">
-        <v>1</v>
+      <c r="Q66" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7255,10 +7255,10 @@
         <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="P71" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q71" s="10" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7969,8 +7969,8 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K77" s="4" t="n">
         <v>-1</v>
@@ -8163,14 +8163,14 @@
       <c r="S77" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8640,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -9527,8 +9527,8 @@
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="9" t="n">
-        <v>3</v>
+      <c r="V91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9777,10 +9777,10 @@
         <v>11</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10394,8 +10394,8 @@
       <c r="S100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -11370,11 +11370,11 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>3</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>4</v>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q111" s="10" t="n">
         <v>2</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12240,8 +12240,8 @@
       <c r="T119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
+      <c r="U119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V119" s="9" t="n">
         <v>3</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14558,7 +14558,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -14591,7 +14591,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14690,7 +14690,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14723,7 +14723,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14789,7 +14789,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
